--- a/Data/Building/MeetingRoomOne.Projecter001.xlsx
+++ b/Data/Building/MeetingRoomOne.Projecter001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:I127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709255960</v>
+        <v>1711847175</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709258641</v>
+        <v>1711850429</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709261048</v>
+        <v>1711850534</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709262396</v>
+        <v>1711851544</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709267076</v>
+        <v>1711859677</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +681,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709268149</v>
+        <v>1711860777</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +699,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +718,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709269166</v>
+        <v>1711928013</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +736,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +759,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709269179</v>
+        <v>1711930312</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +777,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +796,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709249522</v>
+        <v>1711930643</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +814,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +837,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709250775</v>
+        <v>1711932292</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +855,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +874,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709258327</v>
+        <v>1711936118</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +892,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +915,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709259281</v>
+        <v>1711937991</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +933,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +952,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709336431</v>
+        <v>1712014750</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +970,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +993,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709339114</v>
+        <v>1712016962</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +1011,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1030,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709339333</v>
+        <v>1712017285</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1048,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1071,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709340136</v>
+        <v>1712017433</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1089,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1108,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709344294</v>
+        <v>1712018831</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1126,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1149,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709346242</v>
+        <v>1712021053</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1117,6 +1167,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1186,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709346864</v>
+        <v>1712024994</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1204,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1227,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709348298</v>
+        <v>1712025623</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1245,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1264,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709422394</v>
+        <v>1712025819</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1282,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1305,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709424661</v>
+        <v>1712025920</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1323,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1342,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709430721</v>
+        <v>1712102418</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1360,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1383,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709431671</v>
+        <v>1712104063</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1401,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1420,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709431786</v>
+        <v>1712106547</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1369,6 +1438,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1461,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709434358</v>
+        <v>1712109010</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1479,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1498,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709508378</v>
+        <v>1712110992</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1516,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1539,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709509883</v>
+        <v>1712112241</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1477,6 +1557,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1576,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709517008</v>
+        <v>1712113535</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1594,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1617,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709520126</v>
+        <v>1712113601</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1635,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1654,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709520594</v>
+        <v>1712191428</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1585,6 +1672,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1695,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709521575</v>
+        <v>1712193908</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,6 +1713,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1732,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709596589</v>
+        <v>1712195642</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1750,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1769,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709599675</v>
+        <v>1712198521</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1693,6 +1787,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1806,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709608009</v>
+        <v>1712272850</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1729,6 +1824,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1847,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709608889</v>
+        <v>1712274767</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1765,6 +1865,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1884,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709852808</v>
+        <v>1712284181</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1902,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1925,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709855093</v>
+        <v>1712285627</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1943,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1962,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709855665</v>
+        <v>1712537710</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1980,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +2003,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709856509</v>
+        <v>1712537918</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +2021,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +2040,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709862586</v>
+        <v>1712539463</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +2058,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2081,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709863699</v>
+        <v>1712539576</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2099,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2118,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709940571</v>
+        <v>1712545004</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2017,6 +2136,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2159,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709942520</v>
+        <v>1712546295</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2053,6 +2177,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2196,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709943338</v>
+        <v>1712623461</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2214,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2237,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709944952</v>
+        <v>1712623977</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2125,6 +2255,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2274,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709950293</v>
+        <v>1712625127</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2161,6 +2292,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2179,7 +2315,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709951838</v>
+        <v>1712627721</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2197,6 +2333,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2352,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710028016</v>
+        <v>1712628042</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2233,6 +2370,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2393,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710029629</v>
+        <v>1712629651</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2269,6 +2411,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2287,7 +2430,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710029766</v>
+        <v>1712631626</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2305,6 +2448,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2323,7 +2471,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710031628</v>
+        <v>1712632655</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2341,6 +2489,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2508,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710032636</v>
+        <v>1712707865</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2377,6 +2526,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2549,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710035276</v>
+        <v>1712709396</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2413,6 +2567,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2586,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710040544</v>
+        <v>1712711987</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2449,6 +2604,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2623,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710040718</v>
+        <v>1712712911</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2485,6 +2641,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2503,7 +2660,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710115292</v>
+        <v>1712716904</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2521,6 +2678,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2539,7 +2701,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710116318</v>
+        <v>1712719560</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2557,6 +2719,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2575,7 +2738,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710118811</v>
+        <v>1712797391</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2593,6 +2756,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2611,7 +2779,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710120417</v>
+        <v>1712798474</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2629,6 +2797,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2647,7 +2816,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710125693</v>
+        <v>1712804025</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2665,6 +2834,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2683,7 +2857,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710127631</v>
+        <v>1712805464</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2701,6 +2875,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2719,7 +2894,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710201006</v>
+        <v>1712883544</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2737,6 +2912,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2755,7 +2935,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710203244</v>
+        <v>1712884962</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2773,6 +2953,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2791,7 +2972,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710204424</v>
+        <v>1712889669</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2809,6 +2990,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2827,7 +3013,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710205398</v>
+        <v>1712890565</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2845,6 +3031,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2863,7 +3050,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710205743</v>
+        <v>1713137404</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2881,6 +3068,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2899,7 +3091,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710207196</v>
+        <v>1713138676</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2917,6 +3109,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2935,7 +3128,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710210389</v>
+        <v>1713139106</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2953,6 +3146,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2971,7 +3165,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710213655</v>
+        <v>1713140882</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2989,6 +3183,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3007,7 +3202,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710459591</v>
+        <v>1713146304</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3025,6 +3220,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3043,7 +3243,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710461369</v>
+        <v>1713147504</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3061,6 +3261,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3079,7 +3280,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710463311</v>
+        <v>1713223484</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3097,6 +3298,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3115,7 +3321,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710464665</v>
+        <v>1713225245</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3133,6 +3339,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3151,7 +3358,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710470015</v>
+        <v>1713225932</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3169,6 +3376,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3187,7 +3399,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710470206</v>
+        <v>1713226915</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3205,6 +3417,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3223,7 +3436,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710545485</v>
+        <v>1713230282</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3241,6 +3454,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3259,7 +3477,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710547869</v>
+        <v>1713232267</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3277,6 +3495,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3295,7 +3514,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710548599</v>
+        <v>1713310754</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3313,6 +3532,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3331,7 +3555,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710549707</v>
+        <v>1713313595</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3349,6 +3573,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3367,7 +3592,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710555470</v>
+        <v>1713319800</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3385,6 +3610,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3403,7 +3633,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710557338</v>
+        <v>1713319925</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3421,6 +3651,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3439,7 +3670,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710557525</v>
+        <v>1713320282</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3457,6 +3688,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3475,7 +3711,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710558571</v>
+        <v>1713320975</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3493,6 +3729,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3511,7 +3748,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710638923</v>
+        <v>1713397677</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3529,6 +3766,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3547,7 +3789,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710639104</v>
+        <v>1713399592</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3565,6 +3807,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3583,7 +3826,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710644189</v>
+        <v>1713403658</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3601,6 +3844,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3619,7 +3867,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710644540</v>
+        <v>1713404925</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3637,6 +3885,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3655,7 +3904,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710720961</v>
+        <v>1713484678</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3673,6 +3922,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3691,7 +3945,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710721585</v>
+        <v>1713486053</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3709,6 +3963,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3727,7 +3982,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710729441</v>
+        <v>1713488163</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3745,6 +4000,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3763,7 +4019,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710730443</v>
+        <v>1713488182</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3778,9 +4034,10 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3799,7 +4056,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710805959</v>
+        <v>1713491026</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3817,6 +4074,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3835,7 +4097,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710807914</v>
+        <v>1713492336</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3853,6 +4115,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3871,7 +4134,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710815407</v>
+        <v>1713745606</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3889,6 +4152,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3907,7 +4175,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710816760</v>
+        <v>1713745974</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3925,6 +4193,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3943,7 +4212,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1711064093</v>
+        <v>1713750214</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3961,6 +4230,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3979,7 +4253,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1711065640</v>
+        <v>1713752110</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3997,6 +4271,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4015,7 +4290,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1711066231</v>
+        <v>1713828857</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4033,6 +4308,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4051,7 +4331,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1711066873</v>
+        <v>1713832022</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4069,6 +4349,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4087,7 +4368,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1711067213</v>
+        <v>1713837296</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4105,6 +4386,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4123,7 +4409,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1711068272</v>
+        <v>1713839862</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4141,6 +4427,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4159,7 +4446,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1711072652</v>
+        <v>1713840452</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4177,6 +4464,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4195,7 +4487,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1711073941</v>
+        <v>1713842749</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4213,6 +4505,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4231,7 +4524,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1711074071</v>
+        <v>1713915105</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4249,6 +4542,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4267,7 +4565,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1711074655</v>
+        <v>1713917151</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4285,6 +4583,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4303,7 +4602,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1711150340</v>
+        <v>1713922866</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4321,6 +4620,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4339,7 +4643,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1711152580</v>
+        <v>1713924696</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4357,6 +4661,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4375,7 +4680,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1711160463</v>
+        <v>1713925909</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4393,6 +4698,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4411,7 +4721,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1711163338</v>
+        <v>1713927649</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4429,6 +4739,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4447,7 +4758,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1711236340</v>
+        <v>1714000073</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4465,6 +4776,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4483,7 +4799,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1711238170</v>
+        <v>1714002120</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4501,6 +4817,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4519,7 +4836,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1711239838</v>
+        <v>1714003385</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4537,6 +4854,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4555,7 +4877,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1711241378</v>
+        <v>1714003489</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4573,6 +4895,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4591,7 +4914,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1711243035</v>
+        <v>1714004250</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4609,6 +4932,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4627,7 +4951,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1711244437</v>
+        <v>1714006936</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4642,9 +4966,10 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4663,7 +4988,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1711246140</v>
+        <v>1714007322</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4681,6 +5006,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4699,7 +5029,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1711248829</v>
+        <v>1714008790</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4717,6 +5047,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4735,7 +5066,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1711249460</v>
+        <v>1714009596</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4753,6 +5084,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4771,7 +5107,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1711249599</v>
+        <v>1714010026</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4789,6 +5125,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4807,7 +5144,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1711323656</v>
+        <v>1714087689</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4825,6 +5162,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4843,7 +5185,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1711324806</v>
+        <v>1714088670</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4861,6 +5203,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4879,7 +5222,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1711333169</v>
+        <v>1714089543</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4897,6 +5240,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4915,7 +5263,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1711334823</v>
+        <v>1714089561</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4933,6 +5281,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4951,7 +5300,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1711410251</v>
+        <v>1714095789</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4969,6 +5318,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4987,7 +5341,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1711412416</v>
+        <v>1714096747</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -5005,150 +5359,7 @@
           <t>physical</t>
         </is>
       </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Projecter_Operation</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>1711416863</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Projecter001.state: on</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Projecter_Operation</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>1711418663</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Projecter001.state: off</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Projecter_Operation</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>1711420500</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Projecter001.state: on</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Projecter_Operation</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>1711421671</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>MeetingRoomOne.Projecter001.state: off</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
+      <c r="I127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
